--- a/data/trans_orig/IP40_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP40_R-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3773</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1322</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8412</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,99%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1293</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4089</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4490</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,43%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3773</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1287</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8040</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10232</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12205</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7469</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>18828</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14,5%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8,87%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>22,36%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>15865</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10398</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>22425</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10272</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>22407</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>17,54%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>11,5%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>24,8%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12205</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>7347</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>18945</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>14,5%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20735</t>
+          <t>19899</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37188</t>
+          <t>37531</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>25703</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19208</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>32492</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>30,53%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>22,81%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>38,59%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>29831</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>22608</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>38071</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>22546</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>37582</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>32,99%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>42,1%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>25703</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>19198</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>32875</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>30,53%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>45031</t>
+          <t>45744</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>65221</t>
+          <t>66154</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>42510</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>35411</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>50716</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>50,49%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>42,06%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>60,24%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>43440</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>35822</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>51518</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>36174</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>51489</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>48,04%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>39,61%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>56,97%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>42510</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>34477</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>49543</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>50,49%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75784</t>
+          <t>73240</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97140</t>
+          <t>96091</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,03%</t>
         </is>
       </c>
     </row>
@@ -1174,57 +1174,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>84192</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>84192</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>84192</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>90430</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>90430</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>90430</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>84192</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>84192</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>84192</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1291,72 +1291,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45788</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>35688</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>56550</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>9,7%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>7,56%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>11,98%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>32286</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>24059</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>42546</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>24138</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>41809</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>7,34%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>45788</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>36441</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>58371</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>9,7%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>64923</t>
+          <t>65056</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>93563</t>
+          <t>93338</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>87422</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>73744</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>101791</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>18,52%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,62%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>21,56%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>86532</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>73312</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>101354</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>72756</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>99920</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>19,67%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16,67%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,04%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>87422</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>74339</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>101278</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>18,52%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>155470</t>
+          <t>154463</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>193830</t>
+          <t>195793</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>153377</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>137905</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>170408</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>32,49%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>29,21%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>36,09%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>148645</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>132565</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>165088</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>133961</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>164789</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>33,8%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>30,14%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>37,53%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>153377</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>136176</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>169487</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>32,49%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>278572</t>
+          <t>278845</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>326658</t>
+          <t>324405</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,57%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>185539</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167388</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>201818</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>39,3%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>35,45%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>42,75%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>250</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172367</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>154813</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>188136</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>155035</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>189658</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>39,19%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>35,2%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>42,77%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>185539</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>168870</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>204536</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>39,3%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332791</t>
+          <t>331855</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>380420</t>
+          <t>382443</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,94%</t>
         </is>
       </c>
     </row>
@@ -1743,57 +1743,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>472126</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>472126</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>472126</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>637</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>439829</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>439829</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>439829</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>472126</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>472126</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>472126</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1860,72 +1860,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>47049</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>38168</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>57608</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>27,54%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>22,34%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>33,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>46299</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>36866</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>55855</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>36287</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>55464</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>28,36%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>22,58%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>34,21%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>47049</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>37570</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>58049</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>27,54%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>79345</t>
+          <t>78693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>106692</t>
+          <t>106640</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -1973,72 +1973,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>57895</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>48084</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>67936</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>33,89%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>28,14%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>39,76%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>50787</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>41075</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>60987</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>41045</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>60705</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>31,11%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>25,16%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>37,36%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>57895</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>48074</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>68936</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>33,89%</t>
-        </is>
-      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>95615</t>
+          <t>94846</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>123451</t>
+          <t>122377</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,63%</t>
         </is>
       </c>
     </row>
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>41033</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>31389</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>50741</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>24,02%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>18,37%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>29,7%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>41723</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>32279</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>50266</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>32826</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>51030</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>25,56%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>19,77%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>30,79%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>41033</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>31925</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>50361</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>24,02%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70556</t>
+          <t>70097</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96732</t>
+          <t>96256</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>24880</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>17815</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>34248</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>14,56%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>10,43%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>20,04%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>24454</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>17548</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>33278</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>17745</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>32032</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>14,98%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>20,38%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>24880</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>17864</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>33665</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>14,56%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39738</t>
+          <t>39155</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61041</t>
+          <t>60941</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -2312,57 +2312,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>170858</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>170858</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>170858</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>163263</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>163263</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>163263</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>170858</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>170858</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>170858</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2429,72 +2429,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>96610</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>81282</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>112523</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>13,29%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>11,18%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>15,47%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>79878</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>66763</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>94916</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>67947</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>96186</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>11,52%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>9,63%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>13,69%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>96610</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>80507</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>112697</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>13,29%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>157307</t>
+          <t>157578</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>200033</t>
+          <t>197880</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -2542,72 +2542,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>140033</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>176440</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>21,66%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>19,26%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>24,26%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>153184</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>136507</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>168659</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>135422</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>172436</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>22,09%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>19,68%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>24,32%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>157522</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>140823</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>176696</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>21,66%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>284222</t>
+          <t>284337</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>336993</t>
+          <t>336313</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -2655,72 +2655,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>220114</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>200746</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>243371</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>30,27%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>27,61%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>33,47%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>318</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>220199</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>200493</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>239882</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>201026</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>241465</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>31,75%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>28,91%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>34,59%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>220114</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>198853</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>238985</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>30,27%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>415270</t>
+          <t>412055</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>470324</t>
+          <t>473454</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -2768,72 +2768,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>252929</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>230389</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>274840</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>34,78%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>31,68%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>37,8%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>240261</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>219136</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>260166</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>220121</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>261615</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>34,64%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>31,6%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>37,51%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>252929</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>231978</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>275826</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>34,78%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>462895</t>
+          <t>459751</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>521252</t>
+          <t>524992</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -2881,57 +2881,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>727176</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>727176</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>727176</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>999</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>693522</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>693522</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>693522</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>727176</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>727176</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>727176</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3050,7 +3050,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3061,7 +3061,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3229,72 +3229,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3138</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>885</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7322</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,77%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>571</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2842</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3138</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>731</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7249</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -3342,72 +3342,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3417</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1287</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7480</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5,03%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>11,01%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2724</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>782</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6652</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6134</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>11,71%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>3417</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1246</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>7591</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>11394</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -3455,72 +3455,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13790</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9237</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20759</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>20,29%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>13,59%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>30,55%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>9676</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5505</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15226</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>6091</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>14776</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>17,03%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>26,8%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>13790</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>8809</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>20360</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>20,29%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16831</t>
+          <t>16894</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31080</t>
+          <t>30652</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,57%</t>
         </is>
       </c>
     </row>
@@ -3568,72 +3568,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>47607</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>40708</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>52996</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>70,06%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>59,91%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>77,99%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>43838</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>38504</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>48670</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>38213</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>48558</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>77,17%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>67,78%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>85,67%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>47607</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>40442</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>53849</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>70,06%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>83492</t>
+          <t>83665</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>99251</t>
+          <t>99551</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,79%</t>
         </is>
       </c>
     </row>
@@ -3681,57 +3681,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>67952</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>67952</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>67952</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>56809</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>56809</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>56809</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>67952</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>67952</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>67952</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3798,72 +3798,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>39758</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>31324</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>50560</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>8,23%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>6,48%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>10,46%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>32140</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>24676</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>42787</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>23618</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>41811</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>6,89%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>39758</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>30399</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>51248</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>8,23%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>59505</t>
+          <t>58179</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>86456</t>
+          <t>86465</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -3911,72 +3911,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>81790</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>67893</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>96196</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16,93%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14,05%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>19,91%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>98177</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>84750</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>112125</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>84229</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>111969</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>21,04%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18,16%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,03%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>81790</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>69708</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>96410</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>16,93%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>161012</t>
+          <t>161136</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>199313</t>
+          <t>199708</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -4024,72 +4024,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>146523</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>130566</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>164858</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>30,33%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>27,02%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>34,12%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>144554</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>127914</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>160508</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>127807</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>159480</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>30,98%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>27,41%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>34,4%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>146523</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>129719</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>163204</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>30,33%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>268409</t>
+          <t>268695</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>316055</t>
+          <t>316654</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,34%</t>
         </is>
       </c>
     </row>
@@ -4137,72 +4137,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>215069</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>196508</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>233515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>44,51%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>40,67%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>48,33%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>294</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>191789</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>175664</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>173650</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>206817</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>41,1%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>37,64%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>45,13%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>215069</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>196508</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>231414</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>44,51%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>377646</t>
+          <t>382058</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>430553</t>
+          <t>433072</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,6%</t>
         </is>
       </c>
     </row>
@@ -4250,57 +4250,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>483141</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>483141</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>483141</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>705</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>466659</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>466659</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>466659</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>483141</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>483141</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>483141</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4367,72 +4367,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>58555</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>48043</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>69500</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>31,23%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>25,62%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>37,07%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>46620</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>37108</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>56894</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>37802</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>57012</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>27,18%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>21,63%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>33,16%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>58555</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>48621</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>69810</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>31,23%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91352</t>
+          <t>91792</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119520</t>
+          <t>120134</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -4480,72 +4480,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>63619</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>53467</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>74458</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>33,93%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>28,52%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>39,71%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>54298</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>44669</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>63574</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>45253</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>65056</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>31,65%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>26,04%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>37,06%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>63619</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>53516</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>75122</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>33,93%</t>
-        </is>
-      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>103082</t>
+          <t>102718</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>133467</t>
+          <t>132255</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4575,12 +4575,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>36,84%</t>
         </is>
       </c>
     </row>
@@ -4593,72 +4593,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>39796</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>31984</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>50487</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>21,23%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>17,06%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>26,93%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>44744</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>35674</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>54464</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>35237</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>54491</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>26,08%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>20,8%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>31,75%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>39796</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>31758</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>49820</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>21,23%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71829</t>
+          <t>71459</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98202</t>
+          <t>98007</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -4706,72 +4706,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>25525</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18421</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>34009</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>13,61%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>9,82%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>18,14%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>25887</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>19059</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>33860</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>19040</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>35470</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>15,09%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>11,11%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>19,74%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>25525</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>19073</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>34265</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>13,61%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41623</t>
+          <t>41408</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63664</t>
+          <t>63039</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,56%</t>
         </is>
       </c>
     </row>
@@ -4819,57 +4819,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>171549</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>171549</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>171549</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4936,72 +4936,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>101452</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>86722</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>118110</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>13,74%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>11,74%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>15,99%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>79330</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>67339</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>94579</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>67397</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>93744</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>11,41%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>13,61%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>101452</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>85831</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>116983</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>13,74%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>161412</t>
+          <t>162272</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>202008</t>
+          <t>201835</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -5049,72 +5049,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>148826</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>131177</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>167912</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>20,15%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>17,76%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>22,73%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>155199</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>136679</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>173983</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>136617</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>173374</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>22,33%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>19,67%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>25,03%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>148826</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>132477</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>166536</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>20,15%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>278243</t>
+          <t>279598</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>327684</t>
+          <t>331289</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -5162,72 +5162,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>200109</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>178478</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>219557</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>27,09%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>24,16%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>29,73%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>299</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>198974</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>180552</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>217622</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>180243</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>219371</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>28,63%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>25,98%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>31,31%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>200109</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>181088</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>221008</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>27,09%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>369390</t>
+          <t>371170</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>426279</t>
+          <t>426010</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,72%</t>
         </is>
       </c>
     </row>
@@ -5275,72 +5275,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>288201</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>266748</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>311696</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>39,02%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>36,12%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>42,2%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>397</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>261514</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>240986</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>282374</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>239519</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>281761</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>37,63%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>34,67%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>40,63%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>288201</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>264952</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>310680</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>39,02%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>522038</t>
+          <t>520694</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>582052</t>
+          <t>580685</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,51%</t>
         </is>
       </c>
     </row>
@@ -5388,57 +5388,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>738588</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>738588</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>738588</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1046</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>695017</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>695017</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>695017</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1055</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>738588</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>738588</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>738588</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5557,7 +5557,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5568,7 +5568,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5736,72 +5736,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7707</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3880</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14452</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13,88%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6,99%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>26,02%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3917</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1256</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8284</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3788</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14533</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5811,32 +5811,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12004</t>
+          <t>11790</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6566</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18821</t>
+          <t>18882</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -5849,72 +5849,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7467</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3769</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12882</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>13,44%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6,79%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>23,19%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>10929</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5502</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19158</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>20,93%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10,54%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>36,69%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14117</t>
+          <t>14197</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5924,32 +5924,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>19345</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12754</t>
+          <t>10717</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29872</t>
+          <t>23072</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -5962,72 +5962,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22006</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16197</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>29089</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>39,62%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>29,16%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>52,38%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>19152</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>11720</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>30178</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>36,68%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>22,45%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>57,8%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23819</t>
+          <t>15515</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17390</t>
+          <t>9889</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30680</t>
+          <t>21272</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6037,32 +6037,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>42971</t>
+          <t>37521</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32470</t>
+          <t>28434</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55711</t>
+          <t>46182</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>46,26%</t>
         </is>
       </c>
     </row>
@@ -6075,72 +6075,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18360</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12680</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24554</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>33,06%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>22,83%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>44,21%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>18213</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11179</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>26390</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>34,88%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>21,41%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>50,55%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20355</t>
+          <t>15842</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14672</t>
+          <t>10867</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26696</t>
+          <t>21592</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6150,32 +6150,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>38568</t>
+          <t>34201</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29400</t>
+          <t>26410</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50043</t>
+          <t>42478</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>42,55%</t>
         </is>
       </c>
     </row>
@@ -6188,57 +6188,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>55540</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>55540</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>55540</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>52211</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>52211</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>52211</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>60676</t>
+          <t>44285</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60676</t>
+          <t>44285</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60676</t>
+          <t>44285</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,17 +6263,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>112887</t>
+          <t>99825</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>112887</t>
+          <t>99825</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>112887</t>
+          <t>99825</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6305,72 +6305,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>67861</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>53818</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>83605</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>14,65%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>11,62%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>18,05%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>67071</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>53122</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>81525</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>15,18%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>12,02%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>18,45%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>72542</t>
+          <t>67437</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>58565</t>
+          <t>56339</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89095</t>
+          <t>82125</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6380,32 +6380,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>139613</t>
+          <t>135298</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>119616</t>
+          <t>117175</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>161918</t>
+          <t>155783</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -6418,72 +6418,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>148058</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>128095</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>166851</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>31,96%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27,65%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>36,02%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>124681</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>97654</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>143462</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>28,22%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>32,47%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>156022</t>
+          <t>123714</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>135356</t>
+          <t>108111</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>176466</t>
+          <t>139122</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6493,32 +6493,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>280703</t>
+          <t>271772</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>250978</t>
+          <t>248002</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>309381</t>
+          <t>296411</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -6531,72 +6531,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>171607</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>152141</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>197370</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>37,05%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>32,85%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>42,61%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>157443</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>127303</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>177100</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>35,63%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>28,81%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>40,08%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>195446</t>
+          <t>155861</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>171532</t>
+          <t>138102</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>224011</t>
+          <t>172429</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6606,32 +6606,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>352888</t>
+          <t>327468</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>318879</t>
+          <t>300228</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>389086</t>
+          <t>355612</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>40,56%</t>
         </is>
       </c>
     </row>
@@ -6644,72 +6644,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>75682</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>61454</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>93055</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>16,34%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>13,27%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>20,09%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>92654</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>66431</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>162115</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>20,97%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>15,03%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>36,69%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>79902</t>
+          <t>66626</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64873</t>
+          <t>55343</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>95698</t>
+          <t>81859</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6719,32 +6719,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>172557</t>
+          <t>142308</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>142119</t>
+          <t>123337</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>243597</t>
+          <t>162125</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -6757,57 +6757,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>463208</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>463208</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>463208</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>616</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>441849</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>441849</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>441849</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>503912</t>
+          <t>413638</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>503912</t>
+          <t>413638</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>503912</t>
+          <t>413638</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,17 +6832,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>945761</t>
+          <t>876846</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>945761</t>
+          <t>876846</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>945761</t>
+          <t>876846</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6874,72 +6874,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>71134</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>60676</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>83102</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>42,48%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>36,23%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>49,62%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>69861</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>59753</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>79393</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>47,28%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>40,44%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>53,73%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>75822</t>
+          <t>70528</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63496</t>
+          <t>60617</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>89956</t>
+          <t>80343</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6949,32 +6949,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>145682</t>
+          <t>141661</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>130196</t>
+          <t>126598</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>160663</t>
+          <t>156973</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>49,75%</t>
         </is>
       </c>
     </row>
@@ -6987,72 +6987,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>75987</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>64692</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>86884</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>45,38%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>38,63%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>51,88%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>57920</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>48848</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>67758</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>39,2%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>33,06%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>45,86%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>83757</t>
+          <t>57361</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71173</t>
+          <t>46753</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>96756</t>
+          <t>66524</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7062,32 +7062,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>141677</t>
+          <t>133347</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>125858</t>
+          <t>117779</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>157720</t>
+          <t>148709</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,13%</t>
         </is>
       </c>
     </row>
@@ -7100,72 +7100,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16502</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10892</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>24724</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,85%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>14,76%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>16800</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>10960</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>25247</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>11,37%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,42%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>17,09%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18098</t>
+          <t>16865</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>10742</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26088</t>
+          <t>24658</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7175,17 +7175,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>34898</t>
+          <t>33367</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26236</t>
+          <t>24778</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46652</t>
+          <t>43670</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -7218,32 +7218,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7484</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7253,32 +7253,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4729</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10946</t>
+          <t>7318</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7288,32 +7288,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15049</t>
+          <t>13777</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -7326,57 +7326,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>147752</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>147752</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>147752</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>148068</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>148068</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>148068</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,17 +7401,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>330157</t>
+          <t>315530</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>330157</t>
+          <t>315530</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>330157</t>
+          <t>315530</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7443,72 +7443,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>146701</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>129431</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>167129</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>21,38%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>18,86%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>24,36%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>140849</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>120137</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>160633</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>21,95%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>18,72%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>25,03%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>156451</t>
+          <t>142048</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>135155</t>
+          <t>124463</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>179535</t>
+          <t>158322</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7518,32 +7518,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>297299</t>
+          <t>288749</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>264618</t>
+          <t>263215</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>325289</t>
+          <t>316898</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>24,52%</t>
         </is>
       </c>
     </row>
@@ -7556,72 +7556,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>231511</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>207705</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>254703</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>33,74%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>30,27%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>37,12%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>282</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>193530</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>165898</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>216386</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>30,15%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>25,85%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>33,71%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>248195</t>
+          <t>189920</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>224872</t>
+          <t>171917</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273839</t>
+          <t>209198</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7631,32 +7631,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>441724</t>
+          <t>421432</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>403188</t>
+          <t>390402</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>478250</t>
+          <t>447089</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,6%</t>
         </is>
       </c>
     </row>
@@ -7669,72 +7669,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>210116</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>185148</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>235485</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>30,62%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>26,98%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>34,32%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>193395</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>165908</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>218261</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>30,13%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>25,85%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>34,01%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>237362</t>
+          <t>188240</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>210854</t>
+          <t>169075</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>267771</t>
+          <t>206456</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7744,32 +7744,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>430757</t>
+          <t>398356</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>394597</t>
+          <t>368599</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>472332</t>
+          <t>432603</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -7782,72 +7782,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>97882</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>82493</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>115365</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>14,26%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>12,02%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>16,81%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>114040</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>84723</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>191384</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>17,77%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>13,2%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>29,82%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>85783</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>88525</t>
+          <t>71718</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>124340</t>
+          <t>103010</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7857,32 +7857,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>219025</t>
+          <t>183664</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>186424</t>
+          <t>162850</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>322765</t>
+          <t>207367</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -7895,57 +7895,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>686210</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>686210</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>686210</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>908</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>641813</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>641813</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>641813</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>957</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>746993</t>
+          <t>605991</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>746993</t>
+          <t>605991</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>746993</t>
+          <t>605991</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7970,17 +7970,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1388805</t>
+          <t>1292201</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1388805</t>
+          <t>1292201</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1388805</t>
+          <t>1292201</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
